--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136375999</v>
       </c>
       <c r="B2" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136376668</v>
       </c>
       <c r="B3" t="n">
-        <v>92316</v>
+        <v>92319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136376349</v>
       </c>
       <c r="B11" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>136375904</v>
       </c>
       <c r="B13" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136375999</v>
       </c>
       <c r="B2" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136376668</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136376349</v>
       </c>
       <c r="B11" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>136375904</v>
       </c>
       <c r="B13" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136375999</v>
       </c>
       <c r="B2" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136376668</v>
       </c>
       <c r="B3" t="n">
-        <v>92320</v>
+        <v>92325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136376349</v>
       </c>
       <c r="B11" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>136375904</v>
       </c>
       <c r="B13" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136375999</v>
       </c>
       <c r="B2" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136376668</v>
       </c>
       <c r="B3" t="n">
-        <v>92325</v>
+        <v>92327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136376349</v>
       </c>
       <c r="B11" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>136375904</v>
       </c>
       <c r="B13" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136375999</v>
       </c>
       <c r="B2" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136376668</v>
       </c>
       <c r="B3" t="n">
-        <v>92327</v>
+        <v>92329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136376349</v>
       </c>
       <c r="B11" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>136375904</v>
       </c>
       <c r="B13" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 17342-2025 artfynd.xlsx
+++ b/artfynd/A 17342-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136375999</v>
       </c>
       <c r="B2" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136376668</v>
       </c>
       <c r="B3" t="n">
-        <v>92329</v>
+        <v>92331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136376349</v>
       </c>
       <c r="B11" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>136375904</v>
       </c>
       <c r="B13" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
